--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tonsberg_Sandefjord.xls.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tonsberg_Sandefjord.xls.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{BDD7FE9B-B2D2-464A-8860-42941A399592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{222E5D53-4C75-4EA5-8E89-1098137092AE}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{BDD7FE9B-B2D2-464A-8860-42941A399592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D927B3B0-256C-416B-822B-EBEBE27F1974}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B856B024-48C7-4BFF-B5E4-3C408E652A68}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4839" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4986" uniqueCount="115">
   <si>
     <t>CAR_ID</t>
   </si>
@@ -345,6 +345,42 @@
   </si>
   <si>
     <t>kraków</t>
+  </si>
+  <si>
+    <t>Tlumačov</t>
+  </si>
+  <si>
+    <t>SKALLESTAD</t>
+  </si>
+  <si>
+    <t>Nordagutu</t>
+  </si>
+  <si>
+    <t>Hønefoss</t>
+  </si>
+  <si>
+    <t>Åsgårdstrand</t>
+  </si>
+  <si>
+    <t>Lommedalen</t>
+  </si>
+  <si>
+    <t>Færder</t>
+  </si>
+  <si>
+    <t>Husøysund</t>
+  </si>
+  <si>
+    <t>TØNSBERG</t>
+  </si>
+  <si>
+    <t>Ålgård</t>
+  </si>
+  <si>
+    <t>åsgårdstrand</t>
+  </si>
+  <si>
+    <t>Vear</t>
   </si>
 </sst>
 </file>
@@ -767,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA55DC7-B8AA-4BA7-B767-B74C300660C5}">
-  <dimension ref="A1:J1616"/>
+  <dimension ref="A1:J1665"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40.28515625" customWidth="1"/>
@@ -42854,7 +42890,1287 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1617" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1617" s="2">
+        <v>1499104</v>
+      </c>
+      <c r="B1617" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1617" s="2">
+        <v>10368511</v>
+      </c>
+      <c r="D1617" s="2">
+        <v>6704329</v>
+      </c>
+      <c r="E1617" s="5">
+        <v>46235.916666666664</v>
+      </c>
+      <c r="F1617" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1617" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1617" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1618" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1618" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1618" s="2">
+        <v>10364651</v>
+      </c>
+      <c r="D1618" s="2">
+        <v>5773627</v>
+      </c>
+      <c r="E1618" s="5">
+        <v>46235.916666666664</v>
+      </c>
+      <c r="F1618" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1618" s="2">
+        <v>47</v>
+      </c>
+      <c r="H1618" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1619" s="2">
+        <v>1522893</v>
+      </c>
+      <c r="B1619" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1619" s="2">
+        <v>10287252</v>
+      </c>
+      <c r="D1619" s="2">
+        <v>8114802</v>
+      </c>
+      <c r="E1619" s="5">
+        <v>46239.916666666664</v>
+      </c>
+      <c r="F1619" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1619" s="2">
+        <v>47</v>
+      </c>
+      <c r="H1619" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1620" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1620" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1620" s="2">
+        <v>10382685</v>
+      </c>
+      <c r="D1620" s="2">
+        <v>6594929</v>
+      </c>
+      <c r="E1620" s="5">
+        <v>46239.916666666664</v>
+      </c>
+      <c r="F1620" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1620" s="2">
+        <v>38</v>
+      </c>
+      <c r="H1620" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1621" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1621" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1621" s="2">
+        <v>10383333</v>
+      </c>
+      <c r="D1621" s="2">
+        <v>8211440</v>
+      </c>
+      <c r="E1621" s="5">
+        <v>46240.916666666664</v>
+      </c>
+      <c r="F1621" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1621" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1621" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1622" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1622" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1622" s="2">
+        <v>10387375</v>
+      </c>
+      <c r="D1622" s="2">
+        <v>6223600</v>
+      </c>
+      <c r="E1622" s="5">
+        <v>46241.916666666664</v>
+      </c>
+      <c r="F1622" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1622" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1622" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1623" s="2">
+        <v>1522893</v>
+      </c>
+      <c r="B1623" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1623" s="2">
+        <v>10383738</v>
+      </c>
+      <c r="D1623" s="2">
+        <v>8217573</v>
+      </c>
+      <c r="E1623" s="5">
+        <v>46243.416666666664</v>
+      </c>
+      <c r="F1623" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1623" s="2">
+        <v>69</v>
+      </c>
+      <c r="H1623" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1624" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1624" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1624" s="2">
+        <v>10387326</v>
+      </c>
+      <c r="D1624" s="2">
+        <v>8221637</v>
+      </c>
+      <c r="E1624" s="5">
+        <v>46245.916666666664</v>
+      </c>
+      <c r="F1624" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1624" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1624" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1625" s="2">
+        <v>1522893</v>
+      </c>
+      <c r="B1625" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1625" s="2">
+        <v>10363049</v>
+      </c>
+      <c r="D1625" s="2">
+        <v>8194934</v>
+      </c>
+      <c r="E1625" s="5">
+        <v>46247.416666666664</v>
+      </c>
+      <c r="F1625" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1625" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1625" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1626" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1626" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1626" s="2">
+        <v>10399704</v>
+      </c>
+      <c r="D1626" s="2">
+        <v>3989020</v>
+      </c>
+      <c r="E1626" s="5">
+        <v>46247.416666666664</v>
+      </c>
+      <c r="F1626" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1626" s="2">
+        <v>66</v>
+      </c>
+      <c r="H1626" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1627" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1627" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1627" s="2">
+        <v>10399073</v>
+      </c>
+      <c r="D1627" s="2">
+        <v>8236227</v>
+      </c>
+      <c r="E1627" s="5">
+        <v>46247.916666666664</v>
+      </c>
+      <c r="F1627" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1627" s="2">
+        <v>60</v>
+      </c>
+      <c r="H1627" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1628" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1628" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1628" s="2">
+        <v>10405070</v>
+      </c>
+      <c r="D1628" s="2">
+        <v>8243459</v>
+      </c>
+      <c r="E1628" s="5">
+        <v>46250.416666666664</v>
+      </c>
+      <c r="F1628" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1628" s="2">
+        <v>55</v>
+      </c>
+      <c r="H1628" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1629" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1629" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1629" s="2">
+        <v>10404883</v>
+      </c>
+      <c r="D1629" s="2">
+        <v>4067413</v>
+      </c>
+      <c r="E1629" s="5">
+        <v>46252.416666666664</v>
+      </c>
+      <c r="F1629" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1629" s="2">
+        <v>35</v>
+      </c>
+      <c r="H1629" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1630" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1630" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1630" s="2">
+        <v>10415506</v>
+      </c>
+      <c r="D1630" s="2">
+        <v>7760917</v>
+      </c>
+      <c r="E1630" s="5">
+        <v>46254.416666666664</v>
+      </c>
+      <c r="F1630" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1630" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1630" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1631" s="2">
+        <v>1499104</v>
+      </c>
+      <c r="B1631" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1631" s="2">
+        <v>10418213</v>
+      </c>
+      <c r="D1631" s="2">
+        <v>4722934</v>
+      </c>
+      <c r="E1631" s="5">
+        <v>46255.916666666664</v>
+      </c>
+      <c r="F1631" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1631" s="2">
+        <v>38</v>
+      </c>
+      <c r="H1631" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1632" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1632" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1632" s="2">
+        <v>10421852</v>
+      </c>
+      <c r="D1632" s="2">
+        <v>7162424</v>
+      </c>
+      <c r="E1632" s="5">
+        <v>46257.916666666664</v>
+      </c>
+      <c r="F1632" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1632" s="2">
+        <v>50</v>
+      </c>
+      <c r="H1632" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1633" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1633" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1633" s="2">
+        <v>10425383</v>
+      </c>
+      <c r="D1633" s="2">
+        <v>8199526</v>
+      </c>
+      <c r="E1633" s="5">
+        <v>46259.916666666664</v>
+      </c>
+      <c r="F1633" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1633" s="2">
+        <v>23</v>
+      </c>
+      <c r="H1633" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1634" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1634" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1634" s="2">
+        <v>10428324</v>
+      </c>
+      <c r="D1634" s="2">
+        <v>7971971</v>
+      </c>
+      <c r="E1634" s="5">
+        <v>46260.916666666664</v>
+      </c>
+      <c r="F1634" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1634" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1634" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1635" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1635" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1635" s="2">
+        <v>10430030</v>
+      </c>
+      <c r="D1635" s="2">
+        <v>6995453</v>
+      </c>
+      <c r="E1635" s="5">
+        <v>46260.916666666664</v>
+      </c>
+      <c r="F1635" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1635" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1635" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1636" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1636" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1636" s="2">
+        <v>10429647</v>
+      </c>
+      <c r="D1636" s="2">
+        <v>8271860</v>
+      </c>
+      <c r="E1636" s="5">
+        <v>46262.916666666664</v>
+      </c>
+      <c r="F1636" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1636" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1636" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1637" s="2">
+        <v>1499104</v>
+      </c>
+      <c r="B1637" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1637" s="2">
+        <v>10438704</v>
+      </c>
+      <c r="D1637" s="2">
+        <v>8121298</v>
+      </c>
+      <c r="E1637" s="5">
+        <v>46264.416666666664</v>
+      </c>
+      <c r="F1637" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1637" s="2">
+        <v>44</v>
+      </c>
+      <c r="H1637" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1638" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1638" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1638" s="2">
+        <v>10439859</v>
+      </c>
+      <c r="D1638" s="2">
+        <v>8236227</v>
+      </c>
+      <c r="E1638" s="5">
+        <v>46264.916666666664</v>
+      </c>
+      <c r="F1638" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1638" s="2">
+        <v>60</v>
+      </c>
+      <c r="H1638" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1639" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1639" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1639" s="2">
+        <v>10439341</v>
+      </c>
+      <c r="D1639" s="2">
+        <v>8281151</v>
+      </c>
+      <c r="E1639" s="5">
+        <v>46265.916666666664</v>
+      </c>
+      <c r="F1639" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1639" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1639" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1640" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1640" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1640" s="2">
+        <v>10366237</v>
+      </c>
+      <c r="D1640" s="2">
+        <v>5888511</v>
+      </c>
+      <c r="E1640" s="5">
+        <v>46235.416666666664</v>
+      </c>
+      <c r="F1640" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1640" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1640" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1641" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1641" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1641" s="2">
+        <v>10373241</v>
+      </c>
+      <c r="D1641" s="2">
+        <v>4199493</v>
+      </c>
+      <c r="E1641" s="5">
+        <v>46238.416666666664</v>
+      </c>
+      <c r="F1641" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1641" s="2">
+        <v>38</v>
+      </c>
+      <c r="H1641" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1642" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1642" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1642" s="2">
+        <v>10383802</v>
+      </c>
+      <c r="D1642" s="2">
+        <v>7962217</v>
+      </c>
+      <c r="E1642" s="5">
+        <v>46240.416666666664</v>
+      </c>
+      <c r="F1642" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1642" s="2">
+        <v>35</v>
+      </c>
+      <c r="H1642" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1643" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1643" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1643" s="2">
+        <v>10380740</v>
+      </c>
+      <c r="D1643" s="2">
+        <v>4580821</v>
+      </c>
+      <c r="E1643" s="5">
+        <v>46240.916666666664</v>
+      </c>
+      <c r="F1643" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1643" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1643" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1644" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1644" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1644" s="2">
+        <v>10383704</v>
+      </c>
+      <c r="D1644" s="2">
+        <v>4073022</v>
+      </c>
+      <c r="E1644" s="5">
+        <v>46242.416666666664</v>
+      </c>
+      <c r="F1644" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1644" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1644" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1645" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1645" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1645" s="2">
+        <v>10388918</v>
+      </c>
+      <c r="D1645" s="2">
+        <v>5335119</v>
+      </c>
+      <c r="E1645" s="5">
+        <v>46242.416666666664</v>
+      </c>
+      <c r="F1645" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1645" s="2">
+        <v>47</v>
+      </c>
+      <c r="H1645" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1646" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1646" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1646" s="2">
+        <v>10387673</v>
+      </c>
+      <c r="D1646" s="2">
+        <v>5215115</v>
+      </c>
+      <c r="E1646" s="5">
+        <v>46242.416666666664</v>
+      </c>
+      <c r="F1646" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1646" s="2">
+        <v>25</v>
+      </c>
+      <c r="H1646" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1647" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1647" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1647" s="2">
+        <v>10384803</v>
+      </c>
+      <c r="D1647" s="2">
+        <v>8218786</v>
+      </c>
+      <c r="E1647" s="5">
+        <v>46243.416666666664</v>
+      </c>
+      <c r="F1647" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1647" s="2">
+        <v>21</v>
+      </c>
+      <c r="H1647" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1648" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1648" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1648" s="2">
+        <v>10389633</v>
+      </c>
+      <c r="D1648" s="2">
+        <v>7061087</v>
+      </c>
+      <c r="E1648" s="5">
+        <v>46246.916666666664</v>
+      </c>
+      <c r="F1648" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1648" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1648" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1649" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1649" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1649" s="2">
+        <v>10401437</v>
+      </c>
+      <c r="D1649" s="2">
+        <v>8211440</v>
+      </c>
+      <c r="E1649" s="5">
+        <v>46247.916666666664</v>
+      </c>
+      <c r="F1649" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1649" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1649" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1650" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1650" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1650" s="2">
+        <v>10399462</v>
+      </c>
+      <c r="D1650" s="2">
+        <v>6981590</v>
+      </c>
+      <c r="E1650" s="5">
+        <v>46248.416666666664</v>
+      </c>
+      <c r="F1650" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1650" s="2">
+        <v>50</v>
+      </c>
+      <c r="H1650" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1651" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1651" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1651" s="2">
+        <v>10396515</v>
+      </c>
+      <c r="D1651" s="2">
+        <v>4073022</v>
+      </c>
+      <c r="E1651" s="5">
+        <v>46248.916666666664</v>
+      </c>
+      <c r="F1651" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1651" s="2">
+        <v>33</v>
+      </c>
+      <c r="H1651" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1652" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1652" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1652" s="2">
+        <v>10211911</v>
+      </c>
+      <c r="D1652" s="2">
+        <v>7235999</v>
+      </c>
+      <c r="E1652" s="5">
+        <v>46251.416666666664</v>
+      </c>
+      <c r="F1652" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1652" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1652" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1653" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1653" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1653" s="2">
+        <v>10358087</v>
+      </c>
+      <c r="D1653" s="2">
+        <v>5317029</v>
+      </c>
+      <c r="E1653" s="5">
+        <v>46251.416666666664</v>
+      </c>
+      <c r="F1653" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1653" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1653" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1654" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1654" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1654" s="2">
+        <v>10408391</v>
+      </c>
+      <c r="D1654" s="2">
+        <v>8247991</v>
+      </c>
+      <c r="E1654" s="5">
+        <v>46251.416666666664</v>
+      </c>
+      <c r="F1654" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1654" s="2">
+        <v>42</v>
+      </c>
+      <c r="H1654" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1655" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1655" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1655" s="2">
+        <v>10411439</v>
+      </c>
+      <c r="D1655" s="2">
+        <v>5581512</v>
+      </c>
+      <c r="E1655" s="5">
+        <v>46252.416666666664</v>
+      </c>
+      <c r="F1655" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1655" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1655" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1656" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1656" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1656" s="2">
+        <v>10411457</v>
+      </c>
+      <c r="D1656" s="2">
+        <v>8194236</v>
+      </c>
+      <c r="E1656" s="5">
+        <v>46252.416666666664</v>
+      </c>
+      <c r="F1656" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1656" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1656" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1657" s="2">
+        <v>1425560</v>
+      </c>
+      <c r="B1657" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1657" s="2">
+        <v>10410384</v>
+      </c>
+      <c r="D1657" s="2">
+        <v>8194236</v>
+      </c>
+      <c r="E1657" s="5">
+        <v>46252.416666666664</v>
+      </c>
+      <c r="F1657" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1657" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1657" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1658" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1658" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1658" s="2">
+        <v>10413971</v>
+      </c>
+      <c r="D1658" s="2">
+        <v>7963539</v>
+      </c>
+      <c r="E1658" s="5">
+        <v>46253.416666666664</v>
+      </c>
+      <c r="F1658" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1658" s="2">
+        <v>49</v>
+      </c>
+      <c r="H1658" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1659" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1659" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1659" s="2">
+        <v>10410525</v>
+      </c>
+      <c r="D1659" s="2">
+        <v>5913784</v>
+      </c>
+      <c r="E1659" s="5">
+        <v>46253.416666666664</v>
+      </c>
+      <c r="F1659" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1659" s="2">
+        <v>49</v>
+      </c>
+      <c r="H1659" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1660" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1660" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1660" s="2">
+        <v>10405227</v>
+      </c>
+      <c r="D1660" s="2">
+        <v>6978743</v>
+      </c>
+      <c r="E1660" s="5">
+        <v>46253.916666666664</v>
+      </c>
+      <c r="F1660" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1660" s="2">
+        <v>30</v>
+      </c>
+      <c r="H1660" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1661" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1661" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1661" s="2">
+        <v>10415364</v>
+      </c>
+      <c r="D1661" s="2">
+        <v>5581512</v>
+      </c>
+      <c r="E1661" s="5">
+        <v>46255.416666666664</v>
+      </c>
+      <c r="F1661" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1661" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1661" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1662" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1662" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1662" s="2">
+        <v>10424916</v>
+      </c>
+      <c r="D1662" s="2">
+        <v>7392674</v>
+      </c>
+      <c r="E1662" s="5">
+        <v>46258.916666666664</v>
+      </c>
+      <c r="F1662" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1662" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1662" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1663" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1663" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1663" s="2">
+        <v>10432522</v>
+      </c>
+      <c r="D1663" s="2">
+        <v>4562368</v>
+      </c>
+      <c r="E1663" s="5">
+        <v>46261.916666666664</v>
+      </c>
+      <c r="F1663" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1663" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1663" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1664" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1664" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1664" s="2">
+        <v>10434956</v>
+      </c>
+      <c r="D1664" s="2">
+        <v>5741588</v>
+      </c>
+      <c r="E1664" s="5">
+        <v>46263.416666666664</v>
+      </c>
+      <c r="F1664" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1664" s="2">
+        <v>50</v>
+      </c>
+      <c r="H1664" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1665" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1665" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1665" s="2">
+        <v>10438495</v>
+      </c>
+      <c r="D1665" s="2">
+        <v>7963539</v>
+      </c>
+      <c r="E1665" s="5">
+        <v>46264.916666666664</v>
+      </c>
+      <c r="F1665" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1665" s="2">
+        <v>49</v>
+      </c>
+      <c r="H1665" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{24007f1f-a397-4c20-bfe2-4e251f78f126}" enabled="1" method="Standard" siteId="{0a8a3b9a-8dcd-4ebc-9305-f971454d49bb}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tonsberg_Sandefjord.xls.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tonsberg_Sandefjord.xls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{BDD7FE9B-B2D2-464A-8860-42941A399592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D927B3B0-256C-416B-822B-EBEBE27F1974}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{BDD7FE9B-B2D2-464A-8860-42941A399592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A45F9B-A50C-420D-9B01-17A8A26E62D1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B856B024-48C7-4BFF-B5E4-3C408E652A68}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B856B024-48C7-4BFF-B5E4-3C408E652A68}"/>
   </bookViews>
   <sheets>
     <sheet name="Tønsberg_Sandefjord" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4986" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5077" uniqueCount="121">
   <si>
     <t>CAR_ID</t>
   </si>
@@ -381,6 +381,24 @@
   </si>
   <si>
     <t>Vear</t>
+  </si>
+  <si>
+    <t>Sverresborg</t>
+  </si>
+  <si>
+    <t>Jeseník</t>
+  </si>
+  <si>
+    <t>Jakobsli</t>
+  </si>
+  <si>
+    <t>Holmestrand</t>
+  </si>
+  <si>
+    <t>tolvsrød</t>
+  </si>
+  <si>
+    <t>Cornelius</t>
   </si>
 </sst>
 </file>
@@ -803,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA55DC7-B8AA-4BA7-B767-B74C300660C5}">
-  <dimension ref="A1:J1665"/>
+  <dimension ref="A1:J1696"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40.28515625" customWidth="1"/>
@@ -44164,6 +44182,812 @@
         <v>15</v>
       </c>
     </row>
+    <row r="1666" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1666" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1666" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1666" s="2">
+        <v>10439699</v>
+      </c>
+      <c r="D1666" s="2">
+        <v>7971971</v>
+      </c>
+      <c r="E1666" s="5">
+        <v>46266.916666666664</v>
+      </c>
+      <c r="F1666" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1666" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1666" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1667" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1667" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1667" s="2">
+        <v>10447692</v>
+      </c>
+      <c r="D1667" s="2">
+        <v>8169336</v>
+      </c>
+      <c r="E1667" s="5">
+        <v>46267.916666666664</v>
+      </c>
+      <c r="F1667" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1667" s="2">
+        <v>22</v>
+      </c>
+      <c r="H1667" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1668" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1668" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1668" s="2">
+        <v>10443819</v>
+      </c>
+      <c r="D1668" s="2">
+        <v>6876601</v>
+      </c>
+      <c r="E1668" s="5">
+        <v>46269.416666666664</v>
+      </c>
+      <c r="F1668" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1668" s="2">
+        <v>53</v>
+      </c>
+      <c r="H1668" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1669" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1669" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1669" s="2">
+        <v>10429046</v>
+      </c>
+      <c r="D1669" s="2">
+        <v>6277067</v>
+      </c>
+      <c r="E1669" s="5">
+        <v>46270.416666666664</v>
+      </c>
+      <c r="F1669" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1669" s="2">
+        <v>50</v>
+      </c>
+      <c r="H1669" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1670" s="2">
+        <v>1499104</v>
+      </c>
+      <c r="B1670" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1670" s="2">
+        <v>10471003</v>
+      </c>
+      <c r="D1670" s="2">
+        <v>7044395</v>
+      </c>
+      <c r="E1670" s="5">
+        <v>46276.416666666664</v>
+      </c>
+      <c r="F1670" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1670" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1670" s="2">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1671" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1671" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1671" s="2">
+        <v>10468557</v>
+      </c>
+      <c r="D1671" s="2">
+        <v>7044395</v>
+      </c>
+      <c r="E1671" s="5">
+        <v>46276.416666666664</v>
+      </c>
+      <c r="F1671" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1671" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1671" s="2">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1672" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1672" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1672" s="2">
+        <v>10471659</v>
+      </c>
+      <c r="D1672" s="2">
+        <v>6401725</v>
+      </c>
+      <c r="E1672" s="5">
+        <v>46276.916666666664</v>
+      </c>
+      <c r="F1672" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1672" s="2">
+        <v>59</v>
+      </c>
+      <c r="H1672" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1673" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1673" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1673" s="2">
+        <v>10473769</v>
+      </c>
+      <c r="D1673" s="2">
+        <v>8256290</v>
+      </c>
+      <c r="E1673" s="5">
+        <v>46277.916666666664</v>
+      </c>
+      <c r="F1673" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1673" s="2">
+        <v>42</v>
+      </c>
+      <c r="H1673" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1674" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1674" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1674" s="2">
+        <v>10481312</v>
+      </c>
+      <c r="D1674" s="2">
+        <v>8351987</v>
+      </c>
+      <c r="E1674" s="5">
+        <v>46283.916666666664</v>
+      </c>
+      <c r="F1674" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1674" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1674" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1675" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1675" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1675" s="2">
+        <v>10492334</v>
+      </c>
+      <c r="D1675" s="2">
+        <v>4251208</v>
+      </c>
+      <c r="E1675" s="5">
+        <v>46285.916666666664</v>
+      </c>
+      <c r="F1675" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1675" s="2">
+        <v>37</v>
+      </c>
+      <c r="H1675" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1676" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1676" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1676" s="2">
+        <v>10493577</v>
+      </c>
+      <c r="D1676" s="2">
+        <v>7971971</v>
+      </c>
+      <c r="E1676" s="5">
+        <v>46287.916666666664</v>
+      </c>
+      <c r="F1676" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1676" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1676" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1677" s="2">
+        <v>1499104</v>
+      </c>
+      <c r="B1677" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1677" s="2">
+        <v>10499131</v>
+      </c>
+      <c r="D1677" s="2">
+        <v>4952403</v>
+      </c>
+      <c r="E1677" s="5">
+        <v>46288.916666666664</v>
+      </c>
+      <c r="F1677" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1677" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1677" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1678" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1678" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1678" s="2">
+        <v>10501522</v>
+      </c>
+      <c r="D1678" s="2">
+        <v>8199254</v>
+      </c>
+      <c r="E1678" s="5">
+        <v>46289.416666666664</v>
+      </c>
+      <c r="F1678" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1678" s="2">
+        <v>59</v>
+      </c>
+      <c r="H1678" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1679" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1679" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1679" s="2">
+        <v>10506496</v>
+      </c>
+      <c r="D1679" s="2">
+        <v>8342374</v>
+      </c>
+      <c r="E1679" s="5">
+        <v>46290.916666666664</v>
+      </c>
+      <c r="F1679" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1679" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1679" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1680" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1680" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1680" s="2">
+        <v>10443407</v>
+      </c>
+      <c r="D1680" s="2">
+        <v>8290269</v>
+      </c>
+      <c r="E1680" s="5">
+        <v>46266.416666666664</v>
+      </c>
+      <c r="F1680" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1680" s="2">
+        <v>45</v>
+      </c>
+      <c r="H1680" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1681" s="2">
+        <v>1087872</v>
+      </c>
+      <c r="B1681" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1681" s="2">
+        <v>10447740</v>
+      </c>
+      <c r="D1681" s="2">
+        <v>8312626</v>
+      </c>
+      <c r="E1681" s="5">
+        <v>46268.416666666664</v>
+      </c>
+      <c r="F1681" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1681" s="2">
+        <v>25</v>
+      </c>
+      <c r="H1681" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1682" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1682" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1682" s="2">
+        <v>10447067</v>
+      </c>
+      <c r="D1682" s="2">
+        <v>4189193</v>
+      </c>
+      <c r="E1682" s="5">
+        <v>46268.916666666664</v>
+      </c>
+      <c r="F1682" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1682" s="2">
+        <v>43</v>
+      </c>
+      <c r="H1682" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1683" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1683" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1683" s="2">
+        <v>10445906</v>
+      </c>
+      <c r="D1683" s="2">
+        <v>8288417</v>
+      </c>
+      <c r="E1683" s="5">
+        <v>46271.916666666664</v>
+      </c>
+      <c r="F1683" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1683" s="2">
+        <v>24</v>
+      </c>
+      <c r="H1683" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1684" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1684" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1684" s="2">
+        <v>10460667</v>
+      </c>
+      <c r="D1684" s="2">
+        <v>8326699</v>
+      </c>
+      <c r="E1684" s="5">
+        <v>46272.916666666664</v>
+      </c>
+      <c r="F1684" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1684" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1684" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1685" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1685" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1685" s="2">
+        <v>10463151</v>
+      </c>
+      <c r="D1685" s="2">
+        <v>8334036</v>
+      </c>
+      <c r="E1685" s="5">
+        <v>46274.916666666664</v>
+      </c>
+      <c r="F1685" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1685" s="2">
+        <v>37</v>
+      </c>
+      <c r="H1685" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1686" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1686" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1686" s="2">
+        <v>10468768</v>
+      </c>
+      <c r="D1686" s="2">
+        <v>8339434</v>
+      </c>
+      <c r="E1686" s="5">
+        <v>46275.916666666664</v>
+      </c>
+      <c r="F1686" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1686" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1686" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1687" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1687" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1687" s="2">
+        <v>10427916</v>
+      </c>
+      <c r="D1687" s="2">
+        <v>5308796</v>
+      </c>
+      <c r="E1687" s="5">
+        <v>46280.916666666664</v>
+      </c>
+      <c r="F1687" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1687" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1687" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1688" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1688" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1688" s="2">
+        <v>10488499</v>
+      </c>
+      <c r="D1688" s="2">
+        <v>8358695</v>
+      </c>
+      <c r="E1688" s="5">
+        <v>46283.916666666664</v>
+      </c>
+      <c r="F1688" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1688" s="2">
+        <v>57</v>
+      </c>
+      <c r="H1688" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1689" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1689" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1689" s="2">
+        <v>10487739</v>
+      </c>
+      <c r="D1689" s="2">
+        <v>7261494</v>
+      </c>
+      <c r="E1689" s="5">
+        <v>46284.916666666664</v>
+      </c>
+      <c r="F1689" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1689" s="2">
+        <v>42</v>
+      </c>
+      <c r="H1689" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1690" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1690" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1690" s="2">
+        <v>10494417</v>
+      </c>
+      <c r="D1690" s="2">
+        <v>7963539</v>
+      </c>
+      <c r="E1690" s="5">
+        <v>46286.916666666664</v>
+      </c>
+      <c r="F1690" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1690" s="2">
+        <v>50</v>
+      </c>
+      <c r="H1690" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1691" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1691" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1691" s="2">
+        <v>10507102</v>
+      </c>
+      <c r="D1691" s="2">
+        <v>6523927</v>
+      </c>
+      <c r="E1691" s="5">
+        <v>46291.416666666664</v>
+      </c>
+      <c r="F1691" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1691" s="2">
+        <v>37</v>
+      </c>
+      <c r="H1691" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1692" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1692" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1692" s="2">
+        <v>10504087</v>
+      </c>
+      <c r="D1692" s="2">
+        <v>5317029</v>
+      </c>
+      <c r="E1692" s="5">
+        <v>46292.916666666664</v>
+      </c>
+      <c r="F1692" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1692" s="2">
+        <v>32</v>
+      </c>
+      <c r="H1692" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1693" s="2">
+        <v>978878</v>
+      </c>
+      <c r="B1693" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1693" s="2">
+        <v>10507990</v>
+      </c>
+      <c r="D1693" s="2">
+        <v>7061087</v>
+      </c>
+      <c r="E1693" s="5">
+        <v>46292.916666666664</v>
+      </c>
+      <c r="F1693" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1693" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1693" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1694" s="2">
+        <v>1309115</v>
+      </c>
+      <c r="B1694" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1694" s="2">
+        <v>10503805</v>
+      </c>
+      <c r="D1694" s="2">
+        <v>7968054</v>
+      </c>
+      <c r="E1694" s="5">
+        <v>46293.416666666664</v>
+      </c>
+      <c r="F1694" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1694" s="2">
+        <v>35</v>
+      </c>
+      <c r="H1694" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1695" s="2">
+        <v>1426642</v>
+      </c>
+      <c r="B1695" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1695" s="2">
+        <v>10512277</v>
+      </c>
+      <c r="D1695" s="2">
+        <v>4659629</v>
+      </c>
+      <c r="E1695" s="5">
+        <v>46293.916666666664</v>
+      </c>
+      <c r="F1695" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1695" s="2">
+        <v>31</v>
+      </c>
+      <c r="H1695" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1696" s="2">
+        <v>1167413</v>
+      </c>
+      <c r="B1696" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1696" s="2">
+        <v>10519063</v>
+      </c>
+      <c r="D1696" s="2">
+        <v>8239475</v>
+      </c>
+      <c r="E1696" s="5">
+        <v>46295.916666666664</v>
+      </c>
+      <c r="F1696" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1696" s="2">
+        <v>26</v>
+      </c>
+      <c r="H1696" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
